--- a/Equivalencia columnas conceptos.xlsx
+++ b/Equivalencia columnas conceptos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Migrated O365 Files\Documentos\Implementaciones\Vigentes en implmentacion\2026\Migraciones\Citibank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC2D505-6726-4304-A057-E54A91BBE7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EB9E40-E012-4873-B680-36491529166E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18810" yWindow="-750" windowWidth="15030" windowHeight="9375" xr2:uid="{FCA418E6-7BC9-4506-BCEA-B41E433CDDB5}"/>
+    <workbookView xWindow="2115" yWindow="705" windowWidth="16650" windowHeight="9795" xr2:uid="{FCA418E6-7BC9-4506-BCEA-B41E433CDDB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Equivalencias" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equivalencias!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equivalencias!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
   <si>
     <t>Sueldo Base FO_1003 Imponible y Tributable</t>
   </si>
@@ -669,6 +669,15 @@
   </si>
   <si>
     <t>Aporte Empleador</t>
+  </si>
+  <si>
+    <t>Préstamo de Licencia FO_6521 No Legal</t>
+  </si>
+  <si>
+    <t>PrestamoLicencia</t>
+  </si>
+  <si>
+    <t>Prestamo de Licencia D</t>
   </si>
 </sst>
 </file>
@@ -772,13 +781,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,8 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF60503-4D87-4255-A85F-89D895BE04DF}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
@@ -1142,7 +1151,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1168,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1176,7 +1185,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1210,7 +1219,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1227,7 +1236,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1244,7 +1253,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1312,7 +1321,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>54</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -1346,7 +1355,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>63</v>
       </c>
@@ -1363,7 +1372,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>150</v>
       </c>
@@ -1397,7 +1406,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -1414,7 +1423,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>165</v>
       </c>
@@ -1448,7 +1457,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>168</v>
       </c>
@@ -1465,7 +1474,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>185</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1499,7 +1508,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>162</v>
       </c>
@@ -1516,7 +1525,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1533,7 +1542,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -1550,7 +1559,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1567,7 +1576,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
@@ -1584,7 +1593,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>45</v>
       </c>
@@ -1601,7 +1610,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>48</v>
       </c>
@@ -1618,7 +1627,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>51</v>
       </c>
@@ -1652,7 +1661,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>148</v>
       </c>
@@ -1669,7 +1678,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>171</v>
       </c>
@@ -1686,7 +1695,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
@@ -1703,7 +1712,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>71</v>
       </c>
@@ -1720,7 +1729,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>78</v>
       </c>
@@ -1737,7 +1746,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>81</v>
       </c>
@@ -1754,7 +1763,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>83</v>
       </c>
@@ -1771,7 +1780,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>92</v>
       </c>
@@ -1788,7 +1797,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>95</v>
       </c>
@@ -1805,7 +1814,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>112</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -1839,7 +1848,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>176</v>
       </c>
@@ -1856,7 +1865,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>73</v>
       </c>
@@ -1873,7 +1882,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>75</v>
       </c>
@@ -1890,7 +1899,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>86</v>
       </c>
@@ -1907,7 +1916,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>89</v>
       </c>
@@ -1924,7 +1933,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>97</v>
       </c>
@@ -1941,7 +1950,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>100</v>
       </c>
@@ -1958,7 +1967,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>103</v>
       </c>
@@ -1975,7 +1984,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>106</v>
       </c>
@@ -1992,7 +2001,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>109</v>
       </c>
@@ -2009,7 +2018,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>115</v>
       </c>
@@ -2026,7 +2035,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>118</v>
       </c>
@@ -2043,7 +2052,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>121</v>
       </c>
@@ -2060,7 +2069,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>124</v>
       </c>
@@ -2077,7 +2086,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
@@ -2094,7 +2103,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>179</v>
       </c>
@@ -2128,7 +2137,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>188</v>
       </c>
@@ -2145,7 +2154,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>66</v>
       </c>
@@ -2162,7 +2171,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>127</v>
       </c>
@@ -2179,7 +2188,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>130</v>
       </c>
@@ -2196,7 +2205,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>133</v>
       </c>
@@ -2213,7 +2222,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>136</v>
       </c>
@@ -2230,7 +2239,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>139</v>
       </c>
@@ -2247,35 +2256,42 @@
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="3" t="s">
         <v>144</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="3" t="s">
         <v>208</v>
       </c>
     </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E67" xr:uid="{4AF60503-4D87-4255-A85F-89D895BE04DF}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Bono Fallecimiento HHA_026 Imponible"/>
-        <filter val="Bono por Fallecimiento FO_1039 Imponible y Tributable"/>
-        <filter val="Diferencia Gratificación FO_1014 Imponible y Tributable"/>
-        <filter val="Diferencia mes anterior DDE_115"/>
-        <filter val="Diferencia Mes Anterior NINT HHA_003"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E1" xr:uid="{4AF60503-4D87-4255-A85F-89D895BE04DF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E68">
     <sortCondition ref="D2:D68"/>
   </sortState>

--- a/Equivalencia columnas conceptos.xlsx
+++ b/Equivalencia columnas conceptos.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Migrated O365 Files\Documentos\Implementaciones\Vigentes en implmentacion\2026\Migraciones\Citibank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EB9E40-E012-4873-B680-36491529166E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F63D524-F119-48DA-945F-F66BF8C1FECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="705" windowWidth="16650" windowHeight="9795" xr2:uid="{FCA418E6-7BC9-4506-BCEA-B41E433CDDB5}"/>
+    <workbookView xWindow="75" yWindow="0" windowWidth="20595" windowHeight="8655" xr2:uid="{FCA418E6-7BC9-4506-BCEA-B41E433CDDB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Equivalencias" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equivalencias!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equivalencias!$A$1:$E$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="222">
   <si>
     <t>Sueldo Base FO_1003 Imponible y Tributable</t>
   </si>
@@ -678,6 +678,36 @@
   </si>
   <si>
     <t>Prestamo de Licencia D</t>
+  </si>
+  <si>
+    <t>Cotización Voluntaria FO_6317 No Legal</t>
+  </si>
+  <si>
+    <t>Seguro Salud Empresa IVA FO_6556 Cálculo</t>
+  </si>
+  <si>
+    <t>Seguro Salud Empresa FO_6553 Cálculo</t>
+  </si>
+  <si>
+    <t>Aporte SS Rentabilidad Protegida FO_6339 Cálculo</t>
+  </si>
+  <si>
+    <t>Aporte FAPP Beneficio años cotizados</t>
+  </si>
+  <si>
+    <t>aporteFAPPBAC</t>
+  </si>
+  <si>
+    <t>Aporte Seguro de Salud Empresa IVA</t>
+  </si>
+  <si>
+    <t>DescSegSaludEmpIVA</t>
+  </si>
+  <si>
+    <t>Aporte Seguro de Salud Empresa</t>
+  </si>
+  <si>
+    <t>DescSegSaludEmpresa</t>
   </si>
 </sst>
 </file>
@@ -781,14 +811,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF60503-4D87-4255-A85F-89D895BE04DF}">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
@@ -1852,16 +1884,16 @@
       <c r="A43" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="8" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2283,15 +2315,82 @@
       <c r="C68" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="3" t="s">
         <v>207</v>
       </c>
     </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" t="s">
+        <v>216</v>
+      </c>
+      <c r="C69" t="s">
+        <v>217</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" t="s">
+        <v>178</v>
+      </c>
+      <c r="D70" t="s">
+        <v>197</v>
+      </c>
+      <c r="E70" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B71" t="s">
+        <v>218</v>
+      </c>
+      <c r="C71" t="s">
+        <v>219</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{4AF60503-4D87-4255-A85F-89D895BE04DF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E68">
     <sortCondition ref="D2:D68"/>
   </sortState>
